--- a/Тест/сравнение_ролей.xlsx
+++ b/Тест/сравнение_ролей.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ДД" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Слабые стороны" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ротации" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Честный урон" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Честный урон ротации" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сводка'!$A$1:$F$8</definedName>
@@ -22,6 +24,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ДД'!$A$1:$K$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Слабые стороны'!$A$1:$E$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ротации'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Честный урон'!$A$1:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Честный урон ротации'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -757,7 +761,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Таблицы ниже на листе «Хилы». Искусность, крит, хоты, Искупление, Выбор света, змея/эхо Ткача, цепь −5%, Энергия Света и Добродетель, Громовой чай, Высвободить жизнь, Прилив. СТ = союзник 0. Область = сумма по 5.</t>
+          <t>Таблицы ниже на листе «Хилы». Искусность, крит, хоты, Искупление, Выбор света, змея/эхо Ткача, цепь −5%, Энергия Света и Добродетель, Громовой чай, Высвободить жизнь, Прилив. Паладин Свет закрывает «срочно одного» Вспышкой/Светом небес, не только ЭС. СТ = союзник 0. Область = сумма по 5.</t>
         </is>
       </c>
     </row>
@@ -980,12 +984,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>1. Рыцарь смерти Кровь → 2. Монах Хмелевар → 3. Воин Защита → 4. Паладин Защита → 5. Друид Страж</t>
+          <t>1. Монах Хмелевар → 2. Рыцарь смерти Кровь → 3. Воин Защита → 4. Паладин Защита → 5. Друид Страж</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>1. Рыцарь смерти Кровь → 2. Монах Хмелевар → 3. Воин Защита → 4. Паладин Защита → 5. Друид Страж</t>
+          <t>1. Монах Хмелевар → 2. Рыцарь смерти Кровь → 3. Воин Защита → 4. Паладин Защита → 5. Друид Страж</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1076,12 +1080,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1. Рыцарь смерти Лёд → 2. Гном-инженер Механист → 3. Охотник Стрельба → 4. Разбойник Бой → 5. Охотник Выживание → 6. Чернокнижник Демонология → 7. Маг Лёд → 8. Чернокнижник Колдовство → 9. Рыцарь смерти Нечестивость → 10. Маг Тайная магия → 11. Шаман Стихии → 12. Охотник Повелитель зверей → 13. Чернокнижник Разрушение → 14. Друид Сила зверя → 15. Друид Баланс → 16. Паладин Воздаяние → 17. Шаман Совершенствование → 18. Воин Неистовство → 19. Монах Танцующий с ветром → 20. Гном-инженер Изобретатель → 21. Разбойник Ликвидация → 22. Разбойник Скрытность → 23. Гном-инженер Сапёр → 24. Воин Оружие → 25. Маг Огонь → 26. Жрец Тьма</t>
+          <t>1. Гном-инженер Механист → 2. Охотник Стрельба → 3. Разбойник Бой → 4. Охотник Выживание → 5. Рыцарь смерти Лёд → 6. Чернокнижник Демонология → 7. Маг Лёд → 8. Чернокнижник Колдовство → 9. Рыцарь смерти Нечестивость → 10. Маг Тайная магия → 11. Шаман Стихии → 12. Охотник Повелитель зверей → 13. Чернокнижник Разрушение → 14. Друид Сила зверя → 15. Друид Баланс → 16. Паладин Воздаяние → 17. Шаман Совершенствование → 18. Воин Неистовство → 19. Монах Танцующий с ветром → 20. Гном-инженер Изобретатель → 21. Разбойник Ликвидация → 22. Разбойник Скрытность → 23. Гном-инженер Сапёр → 24. Воин Оружие → 25. Маг Огонь → 26. Жрец Тьма</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>1. Рыцарь смерти Лёд → 2. Охотник Стрельба → 3. Разбойник Бой → 4. Гном-инженер Механист → 5. Охотник Выживание → 6. Маг Тайная магия → 7. Чернокнижник Колдовство → 8. Чернокнижник Демонология → 9. Шаман Стихии → 10. Маг Лёд → 11. Друид Баланс → 12. Друид Сила зверя → 13. Чернокнижник Разрушение → 14. Рыцарь смерти Нечестивость → 15. Охотник Повелитель зверей → 16. Паладин Воздаяние → 17. Монах Танцующий с ветром → 18. Шаман Совершенствование → 19. Воин Неистовство → 20. Разбойник Скрытность → 21. Разбойник Ликвидация → 22. Гном-инженер Сапёр → 23. Воин Оружие → 24. Маг Огонь → 25. Гном-инженер Изобретатель → 26. Жрец Тьма</t>
+          <t>1. Охотник Стрельба → 2. Разбойник Бой → 3. Гном-инженер Механист → 4. Охотник Выживание → 5. Маг Тайная магия → 6. Чернокнижник Колдовство → 7. Чернокнижник Демонология → 8. Шаман Стихии → 9. Рыцарь смерти Лёд → 10. Маг Лёд → 11. Друид Баланс → 12. Друид Сила зверя → 13. Чернокнижник Разрушение → 14. Рыцарь смерти Нечестивость → 15. Охотник Повелитель зверей → 16. Паладин Воздаяние → 17. Монах Танцующий с ветром → 18. Шаман Совершенствование → 19. Воин Неистовство → 20. Разбойник Скрытность → 21. Разбойник Ликвидация → 22. Гном-инженер Сапёр → 23. Воин Оружие → 24. Маг Огонь → 25. Гном-инженер Изобретатель → 26. Жрец Тьма</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1610,25 +1614,25 @@
         <v>99</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>3.901</v>
+        <v>2.159</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>4.288</v>
+        <v>2.452</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>1.666</v>
+        <v>1.144</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>1.967</v>
+        <v>1.522</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>100</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>87.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>78.7</v>
+        <v>65.2</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ход 8</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1991,7 @@
         <v>100</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>65</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>0</v>
@@ -2390,16 +2394,16 @@
         <v>1080</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>136</v>
+        <v>296.8</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>87.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>188.8</v>
+        <v>171.2</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>83.3</v>
+        <v>193.6</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>0</v>
@@ -2408,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>278.4</v>
+        <v>252.6</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
@@ -2416,10 +2420,10 @@
         </is>
       </c>
       <c r="M31" s="10" t="n">
-        <v>3.901</v>
+        <v>2.159</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>4.288</v>
+        <v>2.452</v>
       </c>
       <c r="O31" s="10" t="n">
         <v>309.6</v>
@@ -2799,16 +2803,16 @@
         <v>2160</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>460.8</v>
+        <v>750.9</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>78.7</v>
+        <v>65.2</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>188.8</v>
+        <v>185.1</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>320.6</v>
+        <v>411.5</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>0</v>
@@ -2817,21 +2821,21 @@
         <v>0</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>247.1</v>
+        <v>140.7</v>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ход 8</t>
         </is>
       </c>
       <c r="M40" s="10" t="n">
-        <v>1.666</v>
+        <v>1.144</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>1.967</v>
+        <v>1.522</v>
       </c>
       <c r="O40" s="10" t="n">
-        <v>307.9</v>
+        <v>280.4</v>
       </c>
       <c r="P40" s="10" t="inlineStr">
         <is>
@@ -3224,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3486,16 +3490,16 @@
         <v>439</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1961.6</v>
+        <v>1620.3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>3923.2</v>
+        <v>3240.6</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>36.6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>163.5</v>
+        <v>135</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -3586,31 +3590,31 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>928.1</v>
+        <v>995.8</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>77.3</v>
+        <v>83</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>1500.8</v>
+        <v>1092.5</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>125.1</v>
+        <v>91</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>3001.6</v>
+        <v>2185</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>х1 FA Гнев карателя → х1 FA Божественная защита → х1 Слово славы → х2 Шок небес → х3 Удар воина Света → х4 Шок небес → х5 Слово славы → х6 Шок небес → х7 FA Божественная защита → х7 Удар воина Света → х8 FA Гнев карателя → х8 Слово славы → х9 Шок небес → х10 Удар воина Света → х11 Слово славы → х12 Шок небес</t>
+          <t>х1 FA Гнев карателя → х1 FA Божественная защита → х1 Слово славы → х2 Шок небес → х3 Вспышка Света → х4 Шок небес → х5 Вспышка Света → х6 Шок небес → х7 FA Божественная защита → х7 Слово славы → х8 FA Гнев карателя → х8 Шок небес → х9 Вспышка Света → х10 Шок небес → х11 Слово славы → х12 Шок небес</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>х1 FA Гнев карателя → х1 FA Божественная защита → х1 Свет зари → х2 Шок небес → х3 Свет зари → х4 Шок небес → х5 Свет зари → х6 Шок небес → х7 FA Божественная защита → х7 Удар воина Света → х8 FA Гнев карателя → х8 Свет зари → х9 Шок небес → х10 Свет зари → х11 Шок небес → х12 Удар воина Света</t>
+          <t>х1 FA Гнев карателя → х1 FA Божественная защита → х1 Слово славы → х2 Шок небес → х3 Вспышка Света → х4 Шок небес → х5 Вспышка Света → х6 Свет зари → х7 FA Божественная защита → х7 Вспышка Света → х8 FA Гнев карателя → х8 Шок небес → х9 Вспышка Света → х10 Свет зари → х11 Вспышка Света → х12 Шок небес</t>
         </is>
       </c>
     </row>
@@ -3626,10 +3630,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>863.6</v>
+        <v>815.9</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>2012.1</v>
@@ -3641,11 +3645,11 @@
         <v>4024.2</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>х1 FA Громовой чай → х1 FA Призыв нефритовой змеи → х1 Заживляющий туман → х2 Окутывающий туман → х3 Удар нефритового лотоса → х4 Удар нефритового лотоса → х5 Окутывающий туман → х6 Удар нефритового лотоса → х7 Удар нефритового лотоса → х8 FA Громовой чай → х8 FA Призыв нефритовой змеи → х8 Окутывающий туман → х9 Заживляющий туман → х10 Удар нефритового лотоса → х11 Окутывающий туман → х12 Удар нефритового лотоса</t>
+          <t>х1 FA Громовой чай → х1 FA Призыв нефритовой змеи → х1 Заживляющий туман → х2 Окутывающий туман → х3 Удар нефритового лотоса → х4 Джаб → х5 Окутывающий туман → х6 Удар нефритового лотоса → х7 Джаб → х8 FA Громовой чай → х8 FA Призыв нефритовой змеи → х8 Окутывающий туман → х9 Заживляющий туман → х10 Удар нефритового лотоса → х11 Окутывающий туман → х12 Джаб</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
@@ -3792,16 +3796,16 @@
         <v>48.4</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>2289.5</v>
+        <v>2036.1</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>190.8</v>
+        <v>169.7</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>4579</v>
+        <v>4072.2</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>3.95</v>
+        <v>3.51</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
@@ -3810,23 +3814,300 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Щит небес → х2 Исповедь во врага → х3 Священный огонь → х4 Кара → х5 FA Архангел → х5 Молитва исцеления → х6 Исповедь во врага → х7 Молитва исцеления → х8 Священный огонь → х9 FA Архангел → х9 Молитва исцеления → х10 FA Исчадие ада → х10 Исповедь во врага → х11 Молитва исцеления → х12 Священный огонь</t>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Щит небес → х2 Исповедь во врага → х3 Священный огонь → х4 Кара → х5 FA Архангел → х5 Молитва исцеления → х6 Исповедь во врага → х7 Священный огонь → х8 простой → х9 FA Архангел → х9 простой → х10 FA Исчадие ада → х10 простой → х11 Щит небес → х12 Исповедь во врага</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Порядок СТ: 1. Паладин Свет → 2. Монах Ткач туманов → 3. Жрец Свет → 4. Шаман Исцеление → 5. Друид Исцеление → 6. Жрец Послушание  ·  область: 1. Жрец Послушание → 2. Друид Исцеление → 3. Шаман Исцеление → 4. Монах Ткач туманов → 5. Жрец Свет → 6. Паладин Свет</t>
-        </is>
+          <t>Порядок СТ: 1. Паладин Свет → 2. Монах Ткач туманов → 3. Жрец Свет → 4. Шаман Исцеление → 5. Друид Исцеление → 6. Жрец Послушание  ·  область: 1. Друид Исцеление → 2. Жрец Послушание → 3. Шаман Исцеление → 4. Монах Ткач туманов → 5. Жрец Свет → 6. Паладин Свет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Мана — 24 хода той же честной ротации. «Сух» = первый ход, когда нужная кнопка не влезла в ману.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Класс</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Спек</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Реген / ход</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>СТ сух</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>СТ мана 12х</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>СТ мана 24х</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>5 раненых сух</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>5 мана 12х</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>5 мана 24х</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Свет</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Послушание</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Свет</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>ход 19</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>ход 21</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>ход 11</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Ткач туманов</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>не сел за 24</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>ход 15</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I7"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <conditionalFormatting sqref="C13:C18">
     <cfRule type="colorScale" priority="1">
@@ -4076,19 +4357,19 @@
         <v>642</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>1560.9</v>
+        <v>1260.7</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3017.1</v>
+        <v>2124</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>53.5</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.43</v>
+        <v>1.96</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -4097,7 +4378,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>х1 FA Ледяной столп → х1 FA Зимний горн → х1 FA Незыблемость льда → х1 Воющий ветер → х2 Воющий ветер → х3 FA Зимний горн → х3 Воющий ветер → х4 Воющий ветер → х5 FA Зимний горн → х5 Воющий ветер → х6 FA Ледяной столп → х6 Воющий ветер → х7 FA Зимний горн → х7 Воющий ветер → х8 Воющий ветер → х9 FA Зимний горн → х9 FA Незыблемость льда → х9 Воющий ветер</t>
+          <t>х1 FA Ледяной столп → х1 FA Зимний горн → х1 FA Незыблемость льда → х1 Воющий ветер → х2 Удар льда → х3 FA Зимний горн → х3 Воющий ветер → х4 Жнец душ → х5 FA Зимний горн → х5 Воющий ветер → х6 FA Ледяной столп → х6 Удар льда → х7 FA Зимний горн → х7 Воющий ветер → х8 Жнец душ → х9 FA Зимний горн → х9 FA Незыблемость льда → х9 Воющий ветер</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -6592,12 +6873,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Щит небес → х2 Исповедь во врага → х3 Священный огонь → х4 Кара → х5 FA Архангел → х5 Молитва исцеления → х6 Исповедь во врага → х7 Молитва исцеления → х8 Священный огонь → х9 FA Архангел → х9 Молитва исцеления → х10 FA Исчадие ада → х10 Исповедь во врага → х11 Молитва исцеления → х12 Священный огонь</t>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Щит небес → х2 Исповедь во врага → х3 Священный огонь → х4 Кара → х5 FA Архангел → х5 Молитва исцеления → х6 Исповедь во врага → х7 Священный огонь → х8 простой → х9 FA Архангел → х9 простой → х10 FA Исчадие ада → х10 простой → х11 Щит небес → х12 Исповедь во врага</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Щит небес → х2 Исповедь во врага → х3 Священный огонь → х4 Кара → х5 FA Архангел → х5 Молитва исцеления → х6 Исповедь во врага → х7 Молитва исцеления → х8 Священный огонь → х9 FA Архангел → х9 Молитва исцеления → х10 FA Исчадие ада → х10 Исповедь во врага → х11 Молитва исцеления → х12 Священный огонь</t>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Щит небес → х2 Исповедь во врага → х3 Священный огонь → х4 Кара → х5 FA Архангел → х5 Молитва исцеления → х6 Исповедь во врага → х7 Священный огонь → х8 простой → х9 FA Архангел → х9 простой → х10 FA Исчадие ада → х10 простой → х11 Щит небес → х12 Исповедь во врага</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6981,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>х1 FA Ледяной столп → х1 FA Зимний горн → х1 FA Незыблемость льда → х1 Воющий ветер → х2 Воющий ветер → х3 FA Зимний горн → х3 Воющий ветер → х4 Воющий ветер → х5 FA Зимний горн → х5 Воющий ветер → х6 FA Ледяной столп → х6 Воющий ветер → х7 FA Зимний горн → х7 Воющий ветер → х8 Воющий ветер → х9 FA Зимний горн → х9 FA Незыблемость льда → х9 Воющий ветер</t>
+          <t>х1 FA Ледяной столп → х1 FA Зимний горн → х1 FA Незыблемость льда → х1 Воющий ветер → х2 Удар льда → х3 FA Зимний горн → х3 Воющий ветер → х4 Жнец душ → х5 FA Зимний горн → х5 Воющий ветер → х6 FA Ледяной столп → х6 Удар льда → х7 FA Зимний горн → х7 Воющий ветер → х8 Жнец душ → х9 FA Зимний горн → х9 FA Незыблемость льда → х9 Воющий ветер</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>х1 FA Ледяной столп → х1 FA Зимний горн → х1 FA Незыблемость льда → х1 Воющий ветер → х2 Воющий ветер → х3 FA Зимний горн → х3 Воющий ветер → х4 Воющий ветер → х5 FA Зимний горн → х5 Воющий ветер → х6 FA Ледяной столп → х6 Воющий ветер → х7 FA Зимний горн → х7 Воющий ветер → х8 Воющий ветер → х9 FA Зимний горн → х9 FA Незыблемость льда → х9 Воющий ветер</t>
+          <t>х1 FA Ледяной столп → х1 FA Зимний горн → х1 FA Незыблемость льда → х1 Воющий ветер → х2 Удар льда → х3 FA Зимний горн → х3 Воющий ветер → х4 Жнец душ → х5 FA Зимний горн → х5 Воющий ветер → х6 FA Ледяной столп → х6 Удар льда → х7 FA Зимний горн → х7 Воющий ветер → х8 Жнец душ → х9 FA Зимний горн → х9 FA Незыблемость льда → х9 Воющий ветер</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7310,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>х1 FA Громовой чай → х1 Восстановление сил → х2 Духовный подъём → х3 Окутывающий туман → х4 Духовный подъём → х5 Заживляющий туман → х6 Восстановление сил → х7 Духовный подъём → х8 FA Громовой чай → х8 Окутывающий туман → х9 Духовный подъём → х10 Заживляющий туман → х11 Восстановление сил → х12 Духовный подъём</t>
+          <t>х1 FA Громовой чай → х1 Восстановление сил → х2 Духовный подъём → х3 Окутывающий туман → х4 Духовный подъём → х5 Заживляющий туман → х6 Восстановление сил → х7 Духовный подъём → х8 FA Громовой чай → х8 Окутывающий туман → х9 Духовный подъём → х10 Танцующий журавль → х11 Восстановление сил → х12 Духовный подъём</t>
         </is>
       </c>
     </row>
@@ -7253,4 +7534,3227 @@
   <autoFilter ref="A1:E38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="56" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Класс</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Спек</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>СТ 12х</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Сумма 5</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Сумма 10</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>5 / СТ</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>10 / 5</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Место СТ</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Место 5</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Место 10</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Ротация 1</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Ротация 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Гном-инженер</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Изобретатель</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>746.4</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>746.4</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>746.4</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>х1 Гномский луч смерти → х2 Поток флюкса → х3 Поток флюкса → х4 Поток флюкса → х5 Гномский луч смерти → х6 Поток флюкса → х7 Поток флюкса → х8 Поток флюкса → х9 Гномский луч смерти → х10 Поток флюкса → х11 Поток флюкса → х12 Поток флюкса</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>х1 Гномский луч смерти → х2 Поток флюкса → х3 Поток флюкса → х4 Поток флюкса → х5 Гномский луч смерти → х6 Поток флюкса → х7 Поток флюкса → х8 Поток флюкса → х9 Гномский луч смерти → х10 Поток флюкса → х11 Поток флюкса → х12 Поток флюкса</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Гном-инженер</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Механист</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>688</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1505.5</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2432</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Разгон → х1 Заклёпочный пистолет → х2 Заклёпочный пистолет → х3 Заклёпочный пистолет → х4 FA Разгон → х4 Удар гаечным ключом → х5 Удар гаечным ключом → х6 Заклёпочный пистолет → х7 FA Разгон → х7 Удар гаечным ключом → х8 Удар гаечным ключом → х9 Заклёпочный пистолет → х10 FA Разгон → х10 Удар гаечным ключом → х11 Заклёпочный пистолет → х12 Удар гаечным ключом</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Разгон → х1 Заклёпочный пистолет → х2 Заклёпочный пистолет → х3 Заклёпочный пистолет → х4 FA Разгон → х4 Удар гаечным ключом → х5 Удар гаечным ключом → х6 Заклёпочный пистолет → х7 FA Разгон → х7 Удар гаечным ключом → х8 Удар гаечным ключом → х9 Заклёпочный пистолет → х10 FA Разгон → х10 Удар гаечным ключом → х11 Заклёпочный пистолет → х12 Удар гаечным ключом</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Охотник</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Повелитель зверей</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>631.2</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1056.8</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1713</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Звериный гнев → х1 FA Быстрая стрельба → х1 Укус змеи → х2 Команда «Взять!» → х3 Чародейский выстрел → х4 Укус змеи → х5 Команда «Взять!» → х6 FA Звериный гнев → х6 Чародейский выстрел → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Зверь → х9 Команда «Взять!» → х10 Укус змеи → х11 FA Звериный гнев → х11 Зверь</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Звериный гнев → х1 FA Быстрая стрельба → х1 Залп → х2 Залп → х3 Залп → х4 Залп → х5 Зверь → х6 FA Звериный гнев → х6 Залп → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Зверь → х9 Залп → х10 Укус змеи → х11 FA Звериный гнев → х11 Зверь</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Рыцарь смерти</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Лёд</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>627.8</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1260.7</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>2124</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ледяной столп → х1 Жнец душ → х2 Уничтожение → х3 Жнец душ → х4 Уничтожение → х5 Жнец душ → х6 FA Ледяной столп → х6 Удар льда → х7 Жнец душ → х8 Уничтожение → х9 Жнец душ → х10 Уничтожение → х11 FA Ледяной столп → х11 Жнец душ → х12 Удар льда</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ледяной столп → х1 Воющий ветер → х2 Жнец душ → х3 Воющий ветер → х4 Удар льда → х5 Воющий ветер → х6 FA Ледяной столп → х6 Жнец душ → х7 Воющий ветер → х8 Удар льда → х9 Воющий ветер → х10 Жнец душ → х11 FA Ледяной столп → х11 Воющий ветер → х12 Удар льда</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Послушание</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>589.9</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>589.9</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>589.9</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Исповедь → х2 Священный огонь → х3 Кара → х4 Исповедь → х5 FA Архангел → х5 Священный огонь → х6 Кара → х7 Исповедь → х8 Священный огонь → х9 FA Архангел → х9 Кара → х10 FA Исчадие ада → х10 Исповедь → х11 Священный огонь</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Исповедь → х2 Священный огонь → х3 Кара → х4 Исповедь → х5 FA Архангел → х5 Священный огонь → х6 Кара → х7 Исповедь → х8 Священный огонь → х9 FA Архангел → х9 Кара → х10 FA Исчадие ада → х10 Исповедь → х11 Священный огонь</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Маг</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Лёд</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>587.3</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1144.5</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>2114.6</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Стылая кровь → х1 Элементаль воды → х2 Глубокая заморозка → х3 Ледяная стрела → х4 Ледяная стрела → х5 Глубокая заморозка → х6 FA Стылая кровь → х6 Ледяная стрела → х7 Элементаль воды → х8 Глубокая заморозка → х9 Ледяная стрела → х10 Ледяная стрела → х11 FA Стылая кровь → х11 Глубокая заморозка → х12 Ледяная стрела</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Стылая кровь → х1 Снежная буря → х2 Снежная буря → х3 Снежная буря → х4 Снежная буря → х5 Снежная буря → х6 FA Стылая кровь → х6 Снежная буря → х7 Снежная буря → х8 Снежная буря → х9 Снежная буря → х10 Снежная буря → х11 FA Стылая кровь → х11 Снежная буря → х12 Ледяной шар</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Танцующий с ветром</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>581.8</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1068.7</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2117.9</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Пиво тигриного глаза → х1 Призыв Сюэня → х2 Лапа тигра → х3 Удар восходящего солнца → х4 FA Пиво тигриного глаза → х4 Лапа тигра → х5 Удар восходящего солнца → х6 Лапа тигра → х7 FA Пиво тигриного глаза → х7 Удар восходящего солнца → х8 Лапа тигра → х9 Удар восходящего солнца → х10 FA Пиво тигриного глаза → х10 Призыв Сюэня → х11 Лапа тигра → х12 Удар восходящего солнца</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Пиво тигриного глаза → х1 Танцующий журавль → х2 Танцующий журавль → х3 Танцующий журавль → х4 FA Пиво тигриного глаза → х4 Танцующий журавль → х5 Танцующий журавль → х6 Танцующий журавль → х7 FA Пиво тигриного глаза → х7 Танцующий журавль → х8 Танцующий журавль → х9 Танцующий журавль → х10 FA Пиво тигриного глаза → х10 Танцующий журавль → х11 Призыв Сюэня → х12 Танцующий журавль</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Охотник</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Стрельба</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>580.2</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1276.7</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>2276.2</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Прицельный выстрел → х2 Прицельный выстрел → х3 Укус змеи → х4 Чародейский выстрел → х5 Верный выстрел → х6 Прицельный выстрел → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Верный выстрел → х9 Прицельный выстрел → х10 Верный выстрел → х11 Прицельный выстрел → х12 Верный выстрел</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Шквал → х2 Залп → х3 Залп → х4 Шквал → х5 Укус змеи → х6 Верный выстрел → х7 FA Быстрая стрельба → х7 Шквал → х8 Залп → х9 Верный выстрел → х10 Шквал → х11 Укус змеи → х12 Чародейский выстрел</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Охотник</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Выживание</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>576.3</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1092.5</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1933.1</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Чёрная стрела → х2 Разрывной выстрел → х3 Укус змеи → х4 Чёрная стрела → х5 Разрывной выстрел → х6 Укус змеи → х7 FA Быстрая стрельба → х7 Чёрная стрела → х8 Выстрел кобры → х9 Разрывной выстрел → х10 Чёрная стрела → х11 Укус змеи → х12 Выстрел кобры</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Взрывная ловушка → х2 Залп → х3 Залп → х4 Взрывная ловушка → х5 Залп → х6 Разрывной выстрел → х7 FA Быстрая стрельба → х7 Выстрел кобры → х8 Взрывная ловушка → х9 Залп → х10 Выстрел кобры → х11 Взрывная ловушка → х12 Залп</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Рыцарь смерти</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Нечестивость</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>566.8</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1140.1</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1826.8</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>х1 Удар Плети → х2 Удар Плети → х3 Удар Плети → х4 Удар Плети → х5 Лик смерти → х6 Удар Плети → х7 Удар Плети → х8 Удар Плети → х9 Удар Плети → х10 Лик смерти → х11 Удар Плети → х12 Удар Плети</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>х1 Вспышка болезни → х2 Смерть и разложение → х3 Удар Плети → х4 Удар Плети → х5 Лик смерти → х6 Удар Плети → х7 Вспышка болезни → х8 Удар Плети → х9 Удар Плети → х10 Смерть и разложение → х11 Лик смерти → х12 Удар Плети</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Стихии</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>534.1</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1068.2</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2136.4</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Взрыв стихий → х2 Выброс лавы → х3 Взрыв стихий → х4 Выброс лавы → х5 Взрыв стихий → х6 FA Перерождение → х6 Выброс лавы → х7 Взрыв стихий → х8 Выброс лавы → х9 Взрыв стихий → х10 Выброс лавы → х11 FA Перерождение → х11 Взрыв стихий → х12 Выброс лавы</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Цепная молния → х2 Цепная молния → х3 Цепная молния → х4 Цепная молния → х5 Цепная молния → х6 FA Перерождение → х6 Цепная молния → х7 Цепная молния → х8 Цепная молния → х9 Цепная молния → х10 Цепная молния → х11 FA Перерождение → х11 Цепная молния → х12 Цепная молния</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Чернокнижник</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Демонология</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>517</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1222</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2054.3</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Метаморфоза → х1 Порча → х2 Стрела Тьмы → х3 Стрела Тьмы → х4 Стрела Тьмы → х5 Порча → х6 FA Метаморфоза → х6 Стрела Тьмы → х7 Стрела Тьмы → х8 Стрела Тьмы → х9 Порча → х10 Стрела Тьмы → х11 FA Метаморфоза → х11 Стрела Тьмы → х12 Стрела Тьмы</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Метаморфоза → х1 Буря Скверны (страж) → х2 Порча → х3 Стрела Тьмы → х4 Буря Скверны (страж) → х5 Длань Гул'дана → х6 FA Метаморфоза → х6 Порча → х7 Буря Скверны (страж) → х8 Стрела Тьмы → х9 Стрела Тьмы → х10 Буря Скверны (страж) → х11 FA Метаморфоза → х11 Длань Гул'дана → х12 Стрела Тьмы</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Воздаяние</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>483.6</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>978</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1659.9</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Инквизиция → х1 Вердикт храмовника → х2 Правосудие → х3 Удар воина Света → х4 Правосудие → х5 FA Инквизиция → х5 Вердикт храмовника → х6 Правосудие → х7 Удар воина Света → х8 Правосудие → х9 FA Инквизиция → х9 Вердикт храмовника → х10 Правосудие → х11 Удар воина Света → х12 Правосудие</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Инквизиция → х1 Божественная буря → х2 Правосудие → х3 Удар воина Света → х4 Правосудие → х5 FA Инквизиция → х5 Божественная буря → х6 Правосудие → х7 Удар воина Света → х8 Правосудие → х9 FA Инквизиция → х9 Божественная буря → х10 Правосудие → х11 Удар воина Света → х12 Правосудие</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Воин</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Неистовство</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>479.9</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1099.9</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ярость берсерка → х1 FA Рывок → х1 Яростный выпад → х2 Яростный выпад → х3 Кровавая жажда → х4 Вихрь → х5 FA Рывок → х5 Вихрь → х6 FA Ярость берсерка → х6 Яростный выпад → х7 Кровавая жажда → х8 Вихрь → х9 FA Рывок → х9 Вихрь → х10 Кровавая жажда → х11 FA Ярость берсерка</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ярость берсерка → х1 FA Рывок → х1 Вихрь → х2 Вихрь → х3 Вихрь → х4 Вихрь → х5 FA Рывок → х5 Вихрь → х6 FA Ярость берсерка → х6 Вихрь → х7 Яростный выпад → х8 Яростный выпад → х9 FA Рывок → х9 Вихрь → х10 Кровавая жажда → х11 FA Ярость берсерка</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>476.5</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1037.4</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>2074.8</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Небесное выравнивание → х1 FA Воплощение → х1 Лунный огонь → х2 Солнечный огонь → х3 Звёздный поток → х4 Звёздный огонь → х5 Лунный огонь → х6 FA Небесное выравнивание → х6 Солнечный огонь → х7 FA Воплощение → х7 Звёздный поток → х8 Звёздный огонь → х9 Звёздный поток → х10 Лунный огонь → х11 FA Небесное выравнивание → х11 Звёздный поток</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Небесное выравнивание → х1 FA Воплощение → х1 Звездопад → х2 Ураган → х3 Ураган → х4 Звездопад → х5 Ураган → х6 FA Небесное выравнивание → х6 Ураган → х7 FA Воплощение → х7 Звездопад → х8 Ураган → х9 Ураган → х10 Звездопад → х11 FA Небесное выравнивание → х11 Ураган</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Совершенствование</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>473.1</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1007.2</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1770.2</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Удар бури → х2 Вскипание лавы → х3 Удар бури → х4 Вскипание лавы → х5 Удар бури → х6 FA Перерождение → х6 Вскипание лавы → х7 Удар бури → х8 Вскипание лавы → х9 Удар бури → х10 Вскипание лавы → х11 FA Перерождение → х11 Удар бури → х12 Вскипание лавы</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Кольцо огня → х2 Удар бури → х3 Кольцо огня → х4 Удар бури → х5 Кольцо огня → х6 FA Перерождение → х6 Удар бури → х7 Кольцо огня → х8 Удар бури → х9 Кольцо огня → х10 Удар бури → х11 FA Перерождение → х11 Кольцо огня → х12 Удар бури</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Чернокнижник</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Колдовство</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1138</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2145.1</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тёмная душа: Знание → х1 FA Сожжение души → х1 Нестабильное колдовство → х2 Агония → х3 Порча → х4 Хватка малефиция → х5 Нестабильное колдовство → х6 Хватка малефиция → х7 FA Тёмная душа: Знание → х7 Агония → х8 Порча → х9 Нестабильное колдовство → х10 Хватка малефиция → х11 Хватка малефиция → х12 Хватка малефиция</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тёмная душа: Знание → х1 FA Сожжение души → х1 Семя порчи → х2 Семя порчи → х3 Семя порчи → х4 Семя порчи → х5 Семя порчи → х6 Семя порчи → х7 FA Тёмная душа: Знание → х7 Семя порчи → х8 Семя порчи → х9 Семя порчи → х10 Семя порчи → х11 Семя порчи → х12 Семя порчи</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Маг</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Тайная магия</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>466</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1087.3</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2174.6</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Мощь тайной магии → х1 FA Присутствие разума → х1 Чародейская вспышка → х2 Чародейская вспышка → х3 Чародейская вспышка → х4 Чародейская вспышка → х5 FA Присутствие разума → х5 Чародейская вспышка → х6 FA Мощь тайной магии → х6 Чародейская вспышка → х7 Чародейская вспышка → х8 Чародейская вспышка → х9 FA Присутствие разума → х9 Чародейская вспышка → х10 Чародейская вспышка → х11 FA Мощь тайной магии</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Мощь тайной магии → х1 FA Присутствие разума → х1 Чародейский взрыв → х2 Чародейский взрыв → х3 Чародейский взрыв → х4 Чародейский взрыв → х5 FA Присутствие разума → х5 Чародейский взрыв → х6 FA Мощь тайной магии → х6 Чародейский взрыв → х7 Чародейский взрыв → х8 Чародейский взрыв → х9 FA Присутствие разума → х9 Чародейский взрыв → х10 Чародейский взрыв → х11 FA Мощь тайной магии</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Воин</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Оружие</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>977.1</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1619.5</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Рывок → х1 Удар колосса → х2 Мощный удар → х3 Мощный удар → х4 Удар колосса → х5 FA Рывок → х5 Мощный удар → х6 Мощный удар → х7 Удар колосса → х8 Мощный удар → х9 FA Рывок → х9 Мощный удар → х10 Удар колосса → х11 Смертельный удар → х12 Мощный удар</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Рывок → х1 Вихрь → х2 Удар колосса → х3 Превосходство → х4 Вихрь → х5 FA Рывок → х5 Удар колосса → х6 Превосходство → х7 Вихрь → х8 Удар колосса → х9 FA Рывок → х9 Превосходство → х10 Вихрь → х11 Удар колосса → х12 Превосходство</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Чернокнижник</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Разрушение</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>451.3</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1046.4</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1962</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>х1 Жертвенный огонь → х2 Поджигание → х3 Испепеление → х4 Жертвенный огонь → х5 Поджигание → х6 Испепеление → х7 Жертвенный огонь → х8 Поджигание → х9 Испепеление → х10 Жертвенный огонь → х11 Поджигание → х12 Испепеление</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>х1 Огненный ливень → х2 Огненный ливень → х3 Огненный ливень → х4 Огненный ливень → х5 Огненный ливень → х6 Огненный ливень → х7 Огненный ливень → х8 Огненный ливень → х9 Огненный ливень → х10 Огненный ливень → х11 Огненный ливень → х12 Огненный ливень</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Сила зверя</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>449.1</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>1044.3</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2021.8</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тигриное неистовство → х1 FA Берсерк → х1 FA Дикий рёв → х1 Глубокая рана → х2 Полоснуть → х3 Полоснуть → х4 FA Тигриное неистовство → х4 Глубокая рана → х5 FA Дикий рёв → х5 Полоснуть → х6 FA Берсерк → х6 Свирепый укус → х7 FA Тигриное неистовство → х7 Глубокая рана → х8 Полоснуть → х9 FA Дикий рёв</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тигриное неистовство → х1 FA Берсерк → х1 FA Дикий рёв → х1 Взбучка → х2 Размах → х3 простой → х4 FA Тигриное неистовство → х4 Взбучка → х5 FA Дикий рёв → х5 Размах → х6 FA Берсерк → х6 простой → х7 FA Тигриное неистовство → х7 Взбучка → х8 Размах → х9 FA Дикий рёв</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Разбойник</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Скрытность</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>445</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>1512</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Танец теней → х1 Кровоизлияние → х2 Внезапный удар → х3 Внезапный удар → х4 Потрошение → х5 FA Танец теней → х5 Кровоизлияние → х6 Внезапный удар → х7 простой → х8 Кровоизлияние → х9 FA Танец теней → х9 Внезапный удар → х10 простой → х11 Потрошение → х12 простой</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Танец теней → х1 Веер клинков → х2 Веер клинков → х3 Веер клинков → х4 Веер клинков → х5 FA Танец теней → х5 Веер клинков → х6 простой → х7 Веер клинков → х8 Кровоизлияние → х9 FA Танец теней → х9 простой → х10 Веер клинков → х11 простой → х12 Веер клинков</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Гном-инженер</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Сапёр</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>407</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>728.1</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1362.5</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Нитро-ускорители → х1 Дистанционный заряд → х2 Дистанционный заряд → х3 Дистанционный заряд → х4 Дистанционный заряд → х5 FA Нитро-ускорители → х5 Липкая бомба → х6 Дистанционный заряд → х7 Липкая бомба → х8 Дистанционный заряд → х9 FA Нитро-ускорители → х9 Липкая бомба → х10 Дистанционный заряд → х11 Липкая бомба → х12 Дистанционный заряд</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Нитро-ускорители → х1 Ракетный залп → х2 Кассетная бомба → х3 Липкая бомба → х4 Шрапнель → х5 Липкая бомба → х6 FA Нитро-ускорители → х6 Липкая бомба → х7 Шрапнель → х8 Липкая бомба → х9 Дистанционный заряд → х10 Липкая бомба → х11 FA Нитро-ускорители → х11 Липкая бомба → х12 Шрапнель</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Тьма</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>406.6</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>915.6</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>1831.2</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>х1 Прикосновение вампира → х2 Слово Тьмы: Смерть → х3 Взрыв разума → х4 Слово Тьмы: Смерть → х5 Прикосновение вампира → х6 Всепожирающая чума → х7 Слово Тьмы: Смерть → х8 Взрыв разума → х9 Слово Тьмы: Смерть → х10 Всепожирающая чума → х11 Слово Тьмы: Смерть → х12 Взрыв разума</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>х1 Пронзание разума → х2 Пронзание разума → х3 Пронзание разума → х4 Пронзание разума → х5 Пронзание разума → х6 Пронзание разума → х7 Пронзание разума → х8 Пронзание разума → х9 Пронзание разума → х10 Пронзание разума → х11 Пронзание разума → х12 Пронзание разума</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Маг</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Огонь</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>402.2</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>888.1</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1529.7</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Манипуляции со временем → х1 Ожог → х2 Огненная глыба → х3 Огненная глыба → х4 Ожог → х5 Огненный шар → х6 FA Манипуляции со временем → х6 Огненный шар → х7 Ожог → х8 Живая бомба → х9 Ожог → х10 Ожог → х11 FA Манипуляции со временем → х11 Ожог → х12 Ожог</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Манипуляции со временем → х1 Огненный столб → х2 Ожог → х3 Огненный столб → х4 Огненная глыба → х5 Огненный столб → х6 FA Манипуляции со временем → х6 Ожог → х7 Огненный столб → х8 Огненный шар → х9 Огненный столб → х10 Ожог → х11 FA Манипуляции со временем → х11 Огненный столб → х12 Огненный шар</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Разбойник</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Бой</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>401.4</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>1024.2</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>1937.5</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Выброс адреналина → х1 FA Шквал клинков → х1 Коварный удар → х2 Коварный удар → х3 Коварный удар → х4 FA Шквал клинков → х4 Череда убийств → х5 Коварный удар → х6 FA Выброс адреналина → х6 Коварный удар → х7 FA Шквал клинков → х7 Пробивающий удар → х8 простой → х9 Потрошение → х10 FA Шквал клинков → х10 Череда убийств</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Выброс адреналина → х1 FA Шквал клинков → х1 Череда убийств → х2 Веер клинков → х3 Веер клинков → х4 FA Шквал клинков → х4 Веер клинков → х5 Пробивающий удар → х6 FA Выброс адреналина → х6 Череда убийств → х7 FA Шквал клинков → х7 Веер клинков → х8 Потрошение → х9 Пробивающий удар → х10 FA Шквал клинков → х10 простой</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Разбойник</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Ликвидация</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>714.3</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Вендетта → х1 Мясорубка → х2 Гаррота → х3 Отравление → х4 Отравление → х5 Мясорубка → х6 FA Вендетта → х6 Ликвидация → х7 Гаррота → х8 Отравление → х9 Мясорубка → х10 простой → х11 FA Вендетта → х11 Отравление → х12 Отравление</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Вендетта → х1 Веер клинков → х2 Веер клинков → х3 Веер клинков → х4 Веер клинков → х5 Веер клинков → х6 FA Вендетта → х6 Ликвидация → х7 Веер клинков → х8 Отравление → х9 Отравление → х10 простой → х11 FA Вендетта → х11 Веер клинков → х12 Отравление</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Защита</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1032.4</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1930.6</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>х1 Щит праведника → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Щит праведника → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Щит праведника → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>х1 Щит праведника → х2 Щит мстителя → х3 Освящение → х4 Щит мстителя → х5 Удар воина Света → х6 Щит мстителя → х7 Удар воина Света → х8 Щит мстителя → х9 Освящение → х10 Щит мстителя → х11 Удар воина Света → х12 Щит праведника</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Ткач туманов</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>811</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1563.1</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Призыв нефритовой змеи → х1 Удар нефритового лотоса → х2 Джаб → х3 Джаб → х4 Удар нефритового лотоса → х5 Джаб → х6 Джаб → х7 Удар нефритового лотоса → х8 FA Призыв нефритовой змеи → х8 Джаб → х9 Джаб → х10 Удар нефритового лотоса → х11 Джаб → х12 Джаб</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Призыв нефритовой змеи → х1 Танцующий журавль → х2 Танцующий журавль → х3 Танцующий журавль → х4 Танцующий журавль → х5 Танцующий журавль → х6 Танцующий журавль → х7 Танцующий журавль → х8 FA Призыв нефритовой змеи → х8 Танцующий журавль → х9 Танцующий журавль → х10 Танцующий журавль → х11 Танцующий журавль → х12 Танцующий журавль</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Хмелевар</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1072.6</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2031.8</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар чёрного лотоса → х2 Джаб → х3 Джаб → х4 Удар чёрного лотоса → х5 Джаб → х6 Джаб → х7 Удар чёрного лотоса → х8 Джаб → х9 Джаб → х10 Удар чёрного лотоса → х11 Джаб → х12 Джаб</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар бочонком → х2 Танцующий журавль → х3 Танцующий журавль → х4 Удар бочонком → х5 Танцующий журавль → х6 Удар чёрного лотоса → х7 Удар бочонком → х8 Джаб → х9 Танцующий журавль → х10 Удар чёрного лотоса → х11 Удар бочонком → х12 Джаб</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Воин</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Защита</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1062.1</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>х1 FA Удар грома → х1 Удар щитом → х2 Удар щитом → х3 FA Удар грома → х3 Удар щитом → х4 Удар щитом → х5 FA Удар грома → х5 Удар щитом → х6 Удар щитом → х7 FA Удар грома → х7 Удар щитом → х8 Удар щитом → х9 FA Удар грома → х9 Удар щитом → х10 Удар щитом → х11 FA Удар грома</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>х1 FA Удар грома → х1 Реванш → х2 Удар щитом → х3 FA Удар грома → х3 Реванш → х4 Удар щитом → х5 FA Удар грома → х5 Реванш → х6 Удар щитом → х7 FA Удар грома → х7 Реванш → х8 Удар щитом → х9 FA Удар грома → х9 Реванш → х10 Удар щитом → х11 FA Удар грома</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Страж</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>287.8</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>732.5</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1220.8</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>х1 Трепка → х2 Трепка → х3 Увечье → х4 Растерзать → х5 Увечье → х6 Трепка → х7 Трепка → х8 Трепка → х9 Трепка → х10 Увечье → х11 Трепка → х12 Трепка</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>х1 Взбучка → х2 Растерзать → х3 Трепка → х4 Взбучка → х5 Трепка → х6 Трепка → х7 Взбучка → х8 Растерзать → х9 Увечье → х10 Взбучка → х11 Растерзать → х12 Трепка</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Рыцарь смерти</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Кровь</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>250.7</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1209.9</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2419.8</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар в сердце → х2 Удар в сердце → х3 Удар в сердце → х4 Удар в сердце → х5 Удар смерти → х6 Удар в сердце → х7 Удар в сердце → х8 Удар в сердце → х9 Удар в сердце → х10 Удар смерти → х11 Удар в сердце → х12 Удар в сердце</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>х1 Смерть и разложение → х2 Вскипание крови → х3 Смерть и разложение → х4 Вскипание крови → х5 Смерть и разложение → х6 Вскипание крови → х7 Смерть и разложение → х8 Вскипание крови → х9 Смерть и разложение → х10 Вскипание крови → х11 Вскипание крови → х12 Вскипание крови</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>х1 Лунный огонь → х2 Гнев → х3 Гнев → х4 Гнев → х5 Лунный огонь → х6 Гнев → х7 Гнев → х8 Гнев → х9 Лунный огонь → х10 Гнев → х11 Гнев → х12 Гнев</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>х1 Лунный огонь → х2 Гнев → х3 Гнев → х4 Гнев → х5 Лунный огонь → х6 Гнев → х7 Гнев → х8 Гнев → х9 Лунный огонь → х10 Гнев → х11 Гнев → х12 Гнев</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Свет</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>х1 Кара → х2 Кара → х3 Кара → х4 Кара → х5 Кара → х6 Кара → х7 Кара → х8 Кара → х9 Кара → х10 Кара → х11 Кара → х12 Кара</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>х1 Кара → х2 Кара → х3 Кара → х4 Кара → х5 Кара → х6 Кара → х7 Кара → х8 Кара → х9 Кара → х10 Кара → х11 Кара → х12 Кара</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Свет</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>х1 Удар воина Света → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Удар воина Света → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Удар воина Света → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>х1 Удар воина Света → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Удар воина Света → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Удар воина Света → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>х1 Огненный шок → х2 Тотем целительного потока → х3 Огненный шок → х4 Тотем целительного потока → х5 Огненный шок → х6 Тотем целительного потока → х7 Огненный шок → х8 Тотем целительного потока → х9 Огненный шок → х10 Тотем целительного потока → х11 Огненный шок → х12 Тотем целительного потока</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>х1 Огненный шок → х2 Тотем целительного потока → х3 Огненный шок → х4 Тотем целительного потока → х5 Огненный шок → х6 Тотем целительного потока → х7 Огненный шок → х8 Тотем целительного потока → х9 Огненный шок → х10 Тотем целительного потока → х11 Огненный шок → х12 Тотем целительного потока</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M38"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Класс</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Спек</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>1 цель</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>5 целей</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>10 целей</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Воин</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Оружие</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Рывок → х1 Удар колосса → х2 Мощный удар → х3 Мощный удар → х4 Удар колосса → х5 FA Рывок → х5 Мощный удар → х6 Мощный удар → х7 Удар колосса → х8 Мощный удар → х9 FA Рывок → х9 Мощный удар → х10 Удар колосса → х11 Смертельный удар → х12 Мощный удар</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Рывок → х1 Вихрь → х2 Удар колосса → х3 Превосходство → х4 Вихрь → х5 FA Рывок → х5 Удар колосса → х6 Превосходство → х7 Вихрь → х8 Удар колосса → х9 FA Рывок → х9 Превосходство → х10 Вихрь → х11 Удар колосса → х12 Превосходство</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Рывок → х1 Вихрь → х2 Удар колосса → х3 Превосходство → х4 Вихрь → х5 FA Рывок → х5 Удар колосса → х6 Превосходство → х7 Вихрь → х8 Удар колосса → х9 FA Рывок → х9 Превосходство → х10 Вихрь → х11 Удар колосса → х12 Превосходство</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Воин</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Неистовство</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ярость берсерка → х1 FA Рывок → х1 Яростный выпад → х2 Яростный выпад → х3 Кровавая жажда → х4 Вихрь → х5 FA Рывок → х5 Вихрь → х6 FA Ярость берсерка → х6 Яростный выпад → х7 Кровавая жажда → х8 Вихрь → х9 FA Рывок → х9 Вихрь → х10 Кровавая жажда → х11 FA Ярость берсерка</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ярость берсерка → х1 FA Рывок → х1 Вихрь → х2 Вихрь → х3 Вихрь → х4 Вихрь → х5 FA Рывок → х5 Вихрь → х6 FA Ярость берсерка → х6 Вихрь → х7 Яростный выпад → х8 Яростный выпад → х9 FA Рывок → х9 Вихрь → х10 Кровавая жажда → х11 FA Ярость берсерка</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ярость берсерка → х1 FA Рывок → х1 Вихрь → х2 Вихрь → х3 Вихрь → х4 Вихрь → х5 FA Рывок → х5 Вихрь → х6 FA Ярость берсерка → х6 Вихрь → х7 Яростный выпад → х8 Яростный выпад → х9 FA Рывок → х9 Вихрь → х10 Кровавая жажда → х11 FA Ярость берсерка</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Воин</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Защита</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>х1 FA Удар грома → х1 Удар щитом → х2 Удар щитом → х3 FA Удар грома → х3 Удар щитом → х4 Удар щитом → х5 FA Удар грома → х5 Удар щитом → х6 Удар щитом → х7 FA Удар грома → х7 Удар щитом → х8 Удар щитом → х9 FA Удар грома → х9 Удар щитом → х10 Удар щитом → х11 FA Удар грома</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>х1 FA Удар грома → х1 Реванш → х2 Удар щитом → х3 FA Удар грома → х3 Реванш → х4 Удар щитом → х5 FA Удар грома → х5 Реванш → х6 Удар щитом → х7 FA Удар грома → х7 Реванш → х8 Удар щитом → х9 FA Удар грома → х9 Реванш → х10 Удар щитом → х11 FA Удар грома</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>х1 FA Удар грома → х1 Реванш → х2 Удар щитом → х3 FA Удар грома → х3 Реванш → х4 Удар щитом → х5 FA Удар грома → х5 Реванш → х6 Удар щитом → х7 FA Удар грома → х7 Реванш → х8 Удар щитом → х9 FA Удар грома → х9 Реванш → х10 Удар щитом → х11 FA Удар грома</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Свет</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>х1 Удар воина Света → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Удар воина Света → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Удар воина Света → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>х1 Удар воина Света → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Удар воина Света → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Удар воина Света → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>х1 Удар воина Света → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Удар воина Света → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Удар воина Света → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Защита</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>х1 Щит праведника → х2 Удар воина Света → х3 Удар воина Света → х4 Удар воина Света → х5 Щит праведника → х6 Удар воина Света → х7 Удар воина Света → х8 Удар воина Света → х9 Щит праведника → х10 Удар воина Света → х11 Удар воина Света → х12 Удар воина Света</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>х1 Щит праведника → х2 Щит мстителя → х3 Освящение → х4 Щит мстителя → х5 Удар воина Света → х6 Щит мстителя → х7 Удар воина Света → х8 Щит мстителя → х9 Освящение → х10 Щит мстителя → х11 Удар воина Света → х12 Щит праведника</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>х1 Щит праведника → х2 Щит мстителя → х3 Освящение → х4 Щит мстителя → х5 Удар воина Света → х6 Щит мстителя → х7 Удар воина Света → х8 Щит мстителя → х9 Освящение → х10 Щит мстителя → х11 Удар воина Света → х12 Щит праведника</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Паладин</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Воздаяние</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Инквизиция → х1 Вердикт храмовника → х2 Правосудие → х3 Удар воина Света → х4 Правосудие → х5 FA Инквизиция → х5 Вердикт храмовника → х6 Правосудие → х7 Удар воина Света → х8 Правосудие → х9 FA Инквизиция → х9 Вердикт храмовника → х10 Правосудие → х11 Удар воина Света → х12 Правосудие</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Инквизиция → х1 Божественная буря → х2 Правосудие → х3 Удар воина Света → х4 Правосудие → х5 FA Инквизиция → х5 Божественная буря → х6 Правосудие → х7 Удар воина Света → х8 Правосудие → х9 FA Инквизиция → х9 Божественная буря → х10 Правосудие → х11 Удар воина Света → х12 Правосудие</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Инквизиция → х1 Божественная буря → х2 Правосудие → х3 Удар воина Света → х4 Правосудие → х5 FA Инквизиция → х5 Божественная буря → х6 Правосудие → х7 Удар воина Света → х8 Правосудие → х9 FA Инквизиция → х9 Божественная буря → х10 Правосудие → х11 Удар воина Света → х12 Правосудие</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Охотник</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Повелитель зверей</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Звериный гнев → х1 FA Быстрая стрельба → х1 Укус змеи → х2 Команда «Взять!» → х3 Чародейский выстрел → х4 Укус змеи → х5 Команда «Взять!» → х6 FA Звериный гнев → х6 Чародейский выстрел → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Зверь → х9 Команда «Взять!» → х10 Укус змеи → х11 FA Звериный гнев → х11 Зверь</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Звериный гнев → х1 FA Быстрая стрельба → х1 Залп → х2 Залп → х3 Залп → х4 Залп → х5 Зверь → х6 FA Звериный гнев → х6 Залп → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Зверь → х9 Залп → х10 Укус змеи → х11 FA Звериный гнев → х11 Зверь</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Звериный гнев → х1 FA Быстрая стрельба → х1 Залп → х2 Залп → х3 Залп → х4 Залп → х5 Зверь → х6 FA Звериный гнев → х6 Залп → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Зверь → х9 Залп → х10 Укус змеи → х11 FA Звериный гнев → х11 Зверь</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Охотник</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Стрельба</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Прицельный выстрел → х2 Прицельный выстрел → х3 Укус змеи → х4 Чародейский выстрел → х5 Верный выстрел → х6 Прицельный выстрел → х7 FA Быстрая стрельба → х7 Укус змеи → х8 Верный выстрел → х9 Прицельный выстрел → х10 Верный выстрел → х11 Прицельный выстрел → х12 Верный выстрел</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Шквал → х2 Залп → х3 Залп → х4 Шквал → х5 Укус змеи → х6 Верный выстрел → х7 FA Быстрая стрельба → х7 Шквал → х8 Залп → х9 Верный выстрел → х10 Шквал → х11 Укус змеи → х12 Чародейский выстрел</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Шквал → х2 Залп → х3 Залп → х4 Шквал → х5 Укус змеи → х6 Верный выстрел → х7 FA Быстрая стрельба → х7 Шквал → х8 Залп → х9 Верный выстрел → х10 Шквал → х11 Укус змеи → х12 Чародейский выстрел</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Охотник</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Выживание</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Чёрная стрела → х2 Разрывной выстрел → х3 Укус змеи → х4 Чёрная стрела → х5 Разрывной выстрел → х6 Укус змеи → х7 FA Быстрая стрельба → х7 Чёрная стрела → х8 Выстрел кобры → х9 Разрывной выстрел → х10 Чёрная стрела → х11 Укус змеи → х12 Выстрел кобры</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Взрывная ловушка → х2 Залп → х3 Залп → х4 Взрывная ловушка → х5 Залп → х6 Разрывной выстрел → х7 FA Быстрая стрельба → х7 Выстрел кобры → х8 Взрывная ловушка → х9 Залп → х10 Выстрел кобры → х11 Взрывная ловушка → х12 Залп</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Быстрая стрельба → х1 Взрывная ловушка → х2 Залп → х3 Залп → х4 Взрывная ловушка → х5 Залп → х6 Разрывной выстрел → х7 FA Быстрая стрельба → х7 Выстрел кобры → х8 Взрывная ловушка → х9 Залп → х10 Выстрел кобры → х11 Взрывная ловушка → х12 Залп</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Разбойник</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Ликвидация</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Вендетта → х1 Мясорубка → х2 Гаррота → х3 Отравление → х4 Отравление → х5 Мясорубка → х6 FA Вендетта → х6 Ликвидация → х7 Гаррота → х8 Отравление → х9 Мясорубка → х10 простой → х11 FA Вендетта → х11 Отравление → х12 Отравление</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Вендетта → х1 Веер клинков → х2 Веер клинков → х3 Веер клинков → х4 Веер клинков → х5 Веер клинков → х6 FA Вендетта → х6 Ликвидация → х7 Веер клинков → х8 Отравление → х9 Отравление → х10 простой → х11 FA Вендетта → х11 Веер клинков → х12 Отравление</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Вендетта → х1 Веер клинков → х2 Веер клинков → х3 Веер клинков → х4 Веер клинков → х5 Веер клинков → х6 FA Вендетта → х6 Отравление → х7 Ликвидация → х8 Веер клинков → х9 Отравление → х10 простой → х11 FA Вендетта → х11 Веер клинков → х12 Отравление</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Разбойник</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Бой</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Выброс адреналина → х1 FA Шквал клинков → х1 Коварный удар → х2 Коварный удар → х3 Коварный удар → х4 FA Шквал клинков → х4 Череда убийств → х5 Коварный удар → х6 FA Выброс адреналина → х6 Коварный удар → х7 FA Шквал клинков → х7 Пробивающий удар → х8 простой → х9 Потрошение → х10 FA Шквал клинков → х10 Череда убийств</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Выброс адреналина → х1 FA Шквал клинков → х1 Череда убийств → х2 Веер клинков → х3 Веер клинков → х4 FA Шквал клинков → х4 Веер клинков → х5 Пробивающий удар → х6 FA Выброс адреналина → х6 Череда убийств → х7 FA Шквал клинков → х7 Веер клинков → х8 Потрошение → х9 Пробивающий удар → х10 FA Шквал клинков → х10 простой</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Выброс адреналина → х1 FA Шквал клинков → х1 Череда убийств → х2 Веер клинков → х3 Веер клинков → х4 FA Шквал клинков → х4 Веер клинков → х5 Пробивающий удар → х6 FA Выброс адреналина → х6 Череда убийств → х7 FA Шквал клинков → х7 Веер клинков → х8 Веер клинков → х9 Пробивающий удар → х10 FA Шквал клинков → х10 простой</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Разбойник</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Скрытность</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Танец теней → х1 Кровоизлияние → х2 Внезапный удар → х3 Внезапный удар → х4 Потрошение → х5 FA Танец теней → х5 Кровоизлияние → х6 Внезапный удар → х7 простой → х8 Кровоизлияние → х9 FA Танец теней → х9 Внезапный удар → х10 простой → х11 Потрошение → х12 простой</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Танец теней → х1 Веер клинков → х2 Веер клинков → х3 Веер клинков → х4 Веер клинков → х5 FA Танец теней → х5 Веер клинков → х6 простой → х7 Веер клинков → х8 Кровоизлияние → х9 FA Танец теней → х9 простой → х10 Веер клинков → х11 простой → х12 Веер клинков</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Танец теней → х1 Веер клинков → х2 Веер клинков → х3 Веер клинков → х4 Веер клинков → х5 FA Танец теней → х5 Веер клинков → х6 простой → х7 Веер клинков → х8 Кровоизлияние → х9 FA Танец теней → х9 простой → х10 Веер клинков → х11 простой → х12 Веер клинков</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Послушание</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Исповедь → х2 Священный огонь → х3 Кара → х4 Исповедь → х5 FA Архангел → х5 Священный огонь → х6 Кара → х7 Исповедь → х8 Священный огонь → х9 FA Архангел → х9 Кара → х10 FA Исчадие ада → х10 Исповедь → х11 Священный огонь</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Исповедь → х2 Священный огонь → х3 Кара → х4 Исповедь → х5 FA Архангел → х5 Священный огонь → х6 Кара → х7 Исповедь → х8 Священный огонь → х9 FA Архангел → х9 Кара → х10 FA Исчадие ада → х10 Исповедь → х11 Священный огонь</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Исчадие ада → х1 FA Архангел → х1 Исповедь → х2 Священный огонь → х3 Кара → х4 Исповедь → х5 FA Архангел → х5 Священный огонь → х6 Кара → х7 Исповедь → х8 Священный огонь → х9 FA Архангел → х9 Кара → х10 FA Исчадие ада → х10 Исповедь → х11 Священный огонь</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Свет</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>х1 Кара → х2 Кара → х3 Кара → х4 Кара → х5 Кара → х6 Кара → х7 Кара → х8 Кара → х9 Кара → х10 Кара → х11 Кара → х12 Кара</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>х1 Кара → х2 Кара → х3 Кара → х4 Кара → х5 Кара → х6 Кара → х7 Кара → х8 Кара → х9 Кара → х10 Кара → х11 Кара → х12 Кара</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>х1 Кара → х2 Кара → х3 Кара → х4 Кара → х5 Кара → х6 Кара → х7 Кара → х8 Кара → х9 Кара → х10 Кара → х11 Кара → х12 Кара</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Жрец</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Тьма</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>х1 Прикосновение вампира → х2 Слово Тьмы: Смерть → х3 Взрыв разума → х4 Слово Тьмы: Смерть → х5 Прикосновение вампира → х6 Всепожирающая чума → х7 Слово Тьмы: Смерть → х8 Взрыв разума → х9 Слово Тьмы: Смерть → х10 Всепожирающая чума → х11 Слово Тьмы: Смерть → х12 Взрыв разума</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>х1 Пронзание разума → х2 Пронзание разума → х3 Пронзание разума → х4 Пронзание разума → х5 Пронзание разума → х6 Пронзание разума → х7 Пронзание разума → х8 Пронзание разума → х9 Пронзание разума → х10 Пронзание разума → х11 Пронзание разума → х12 Пронзание разума</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>х1 Пронзание разума → х2 Пронзание разума → х3 Пронзание разума → х4 Пронзание разума → х5 Пронзание разума → х6 Пронзание разума → х7 Пронзание разума → х8 Пронзание разума → х9 Пронзание разума → х10 Пронзание разума → х11 Пронзание разума → х12 Пронзание разума</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Рыцарь смерти</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Кровь</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар в сердце → х2 Удар в сердце → х3 Удар в сердце → х4 Удар в сердце → х5 Удар смерти → х6 Удар в сердце → х7 Удар в сердце → х8 Удар в сердце → х9 Удар в сердце → х10 Удар смерти → х11 Удар в сердце → х12 Удар в сердце</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>х1 Смерть и разложение → х2 Вскипание крови → х3 Смерть и разложение → х4 Вскипание крови → х5 Смерть и разложение → х6 Вскипание крови → х7 Смерть и разложение → х8 Вскипание крови → х9 Смерть и разложение → х10 Вскипание крови → х11 Вскипание крови → х12 Вскипание крови</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>х1 Смерть и разложение → х2 Вскипание крови → х3 Смерть и разложение → х4 Вскипание крови → х5 Смерть и разложение → х6 Вскипание крови → х7 Смерть и разложение → х8 Вскипание крови → х9 Смерть и разложение → х10 Вскипание крови → х11 Вскипание крови → х12 Вскипание крови</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Рыцарь смерти</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Лёд</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ледяной столп → х1 Жнец душ → х2 Уничтожение → х3 Жнец душ → х4 Уничтожение → х5 Жнец душ → х6 FA Ледяной столп → х6 Удар льда → х7 Жнец душ → х8 Уничтожение → х9 Жнец душ → х10 Уничтожение → х11 FA Ледяной столп → х11 Жнец душ → х12 Удар льда</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ледяной столп → х1 Воющий ветер → х2 Жнец душ → х3 Воющий ветер → х4 Удар льда → х5 Воющий ветер → х6 FA Ледяной столп → х6 Жнец душ → х7 Воющий ветер → х8 Удар льда → х9 Воющий ветер → х10 Жнец душ → х11 FA Ледяной столп → х11 Воющий ветер → х12 Удар льда</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Ледяной столп → х1 Воющий ветер → х2 Жнец душ → х3 Воющий ветер → х4 Удар льда → х5 Воющий ветер → х6 FA Ледяной столп → х6 Жнец душ → х7 Воющий ветер → х8 Удар льда → х9 Воющий ветер → х10 Жнец душ → х11 FA Ледяной столп → х11 Воющий ветер → х12 Удар льда</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Рыцарь смерти</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Нечестивость</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>х1 Удар Плети → х2 Удар Плети → х3 Удар Плети → х4 Удар Плети → х5 Лик смерти → х6 Удар Плети → х7 Удар Плети → х8 Удар Плети → х9 Удар Плети → х10 Лик смерти → х11 Удар Плети → х12 Удар Плети</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>х1 Вспышка болезни → х2 Смерть и разложение → х3 Удар Плети → х4 Удар Плети → х5 Лик смерти → х6 Удар Плети → х7 Вспышка болезни → х8 Удар Плети → х9 Удар Плети → х10 Смерть и разложение → х11 Лик смерти → х12 Удар Плети</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>х1 Вспышка болезни → х2 Смерть и разложение → х3 Удар Плети → х4 Удар Плети → х5 Лик смерти → х6 Удар Плети → х7 Вспышка болезни → х8 Удар Плети → х9 Удар Плети → х10 Смерть и разложение → х11 Лик смерти → х12 Удар Плети</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Стихии</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Взрыв стихий → х2 Выброс лавы → х3 Взрыв стихий → х4 Выброс лавы → х5 Взрыв стихий → х6 FA Перерождение → х6 Выброс лавы → х7 Взрыв стихий → х8 Выброс лавы → х9 Взрыв стихий → х10 Выброс лавы → х11 FA Перерождение → х11 Взрыв стихий → х12 Выброс лавы</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Цепная молния → х2 Цепная молния → х3 Цепная молния → х4 Цепная молния → х5 Цепная молния → х6 FA Перерождение → х6 Цепная молния → х7 Цепная молния → х8 Цепная молния → х9 Цепная молния → х10 Цепная молния → х11 FA Перерождение → х11 Цепная молния → х12 Цепная молния</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Цепная молния → х2 Цепная молния → х3 Цепная молния → х4 Цепная молния → х5 Цепная молния → х6 FA Перерождение → х6 Цепная молния → х7 Цепная молния → х8 Цепная молния → х9 Цепная молния → х10 Цепная молния → х11 FA Перерождение → х11 Цепная молния → х12 Цепная молния</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Совершенствование</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Удар бури → х2 Вскипание лавы → х3 Удар бури → х4 Вскипание лавы → х5 Удар бури → х6 FA Перерождение → х6 Вскипание лавы → х7 Удар бури → х8 Вскипание лавы → х9 Удар бури → х10 Вскипание лавы → х11 FA Перерождение → х11 Удар бури → х12 Вскипание лавы</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Кольцо огня → х2 Удар бури → х3 Кольцо огня → х4 Удар бури → х5 Кольцо огня → х6 FA Перерождение → х6 Удар бури → х7 Кольцо огня → х8 Удар бури → х9 Кольцо огня → х10 Удар бури → х11 FA Перерождение → х11 Кольцо огня → х12 Удар бури</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Перерождение → х1 Кольцо огня → х2 Удар бури → х3 Кольцо огня → х4 Удар бури → х5 Кольцо огня → х6 FA Перерождение → х6 Удар бури → х7 Кольцо огня → х8 Удар бури → х9 Кольцо огня → х10 Удар бури → х11 FA Перерождение → х11 Кольцо огня → х12 Удар бури</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Шаман</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>х1 Огненный шок → х2 Тотем целительного потока → х3 Огненный шок → х4 Тотем целительного потока → х5 Огненный шок → х6 Тотем целительного потока → х7 Огненный шок → х8 Тотем целительного потока → х9 Огненный шок → х10 Тотем целительного потока → х11 Огненный шок → х12 Тотем целительного потока</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>х1 Огненный шок → х2 Тотем целительного потока → х3 Огненный шок → х4 Тотем целительного потока → х5 Огненный шок → х6 Тотем целительного потока → х7 Огненный шок → х8 Тотем целительного потока → х9 Огненный шок → х10 Тотем целительного потока → х11 Огненный шок → х12 Тотем целительного потока</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>х1 Огненный шок → х2 Тотем целительного потока → х3 Огненный шок → х4 Тотем целительного потока → х5 Огненный шок → х6 Тотем целительного потока → х7 Огненный шок → х8 Тотем целительного потока → х9 Огненный шок → х10 Тотем целительного потока → х11 Огненный шок → х12 Тотем целительного потока</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Маг</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Тайная магия</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Мощь тайной магии → х1 FA Присутствие разума → х1 Чародейская вспышка → х2 Чародейская вспышка → х3 Чародейская вспышка → х4 Чародейская вспышка → х5 FA Присутствие разума → х5 Чародейская вспышка → х6 FA Мощь тайной магии → х6 Чародейская вспышка → х7 Чародейская вспышка → х8 Чародейская вспышка → х9 FA Присутствие разума → х9 Чародейская вспышка → х10 Чародейская вспышка → х11 FA Мощь тайной магии</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Мощь тайной магии → х1 FA Присутствие разума → х1 Чародейский взрыв → х2 Чародейский взрыв → х3 Чародейский взрыв → х4 Чародейский взрыв → х5 FA Присутствие разума → х5 Чародейский взрыв → х6 FA Мощь тайной магии → х6 Чародейский взрыв → х7 Чародейский взрыв → х8 Чародейский взрыв → х9 FA Присутствие разума → х9 Чародейский взрыв → х10 Чародейский взрыв → х11 FA Мощь тайной магии</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Мощь тайной магии → х1 FA Присутствие разума → х1 Чародейский взрыв → х2 Чародейский взрыв → х3 Чародейский взрыв → х4 Чародейский взрыв → х5 FA Присутствие разума → х5 Чародейский взрыв → х6 FA Мощь тайной магии → х6 Чародейский взрыв → х7 Чародейский взрыв → х8 Чародейский взрыв → х9 FA Присутствие разума → х9 Чародейский взрыв → х10 Чародейский взрыв → х11 FA Мощь тайной магии</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Маг</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Огонь</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Манипуляции со временем → х1 Ожог → х2 Огненная глыба → х3 Огненная глыба → х4 Ожог → х5 Огненный шар → х6 FA Манипуляции со временем → х6 Огненный шар → х7 Ожог → х8 Живая бомба → х9 Ожог → х10 Ожог → х11 FA Манипуляции со временем → х11 Ожог → х12 Ожог</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Манипуляции со временем → х1 Огненный столб → х2 Ожог → х3 Огненный столб → х4 Огненная глыба → х5 Огненный столб → х6 FA Манипуляции со временем → х6 Ожог → х7 Огненный столб → х8 Огненный шар → х9 Огненный столб → х10 Ожог → х11 FA Манипуляции со временем → х11 Огненный столб → х12 Огненный шар</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Манипуляции со временем → х1 Огненный столб → х2 Ожог → х3 Огненный столб → х4 Огненная глыба → х5 Огненный столб → х6 FA Манипуляции со временем → х6 Ожог → х7 Огненный столб → х8 Огненный шар → х9 Огненный столб → х10 Ожог → х11 FA Манипуляции со временем → х11 Огненный столб → х12 Огненный шар</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Маг</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Лёд</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Стылая кровь → х1 Элементаль воды → х2 Глубокая заморозка → х3 Ледяная стрела → х4 Ледяная стрела → х5 Глубокая заморозка → х6 FA Стылая кровь → х6 Ледяная стрела → х7 Элементаль воды → х8 Глубокая заморозка → х9 Ледяная стрела → х10 Ледяная стрела → х11 FA Стылая кровь → х11 Глубокая заморозка → х12 Ледяная стрела</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Стылая кровь → х1 Снежная буря → х2 Снежная буря → х3 Снежная буря → х4 Снежная буря → х5 Снежная буря → х6 FA Стылая кровь → х6 Снежная буря → х7 Снежная буря → х8 Снежная буря → х9 Снежная буря → х10 Снежная буря → х11 FA Стылая кровь → х11 Снежная буря → х12 Ледяной шар</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Стылая кровь → х1 Снежная буря → х2 Снежная буря → х3 Снежная буря → х4 Снежная буря → х5 Снежная буря → х6 FA Стылая кровь → х6 Снежная буря → х7 Снежная буря → х8 Снежная буря → х9 Снежная буря → х10 Снежная буря → х11 FA Стылая кровь → х11 Снежная буря → х12 Ледяной шар</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Чернокнижник</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Колдовство</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тёмная душа: Знание → х1 FA Сожжение души → х1 Нестабильное колдовство → х2 Агония → х3 Порча → х4 Хватка малефиция → х5 Нестабильное колдовство → х6 Хватка малефиция → х7 FA Тёмная душа: Знание → х7 Агония → х8 Порча → х9 Нестабильное колдовство → х10 Хватка малефиция → х11 Хватка малефиция → х12 Хватка малефиция</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тёмная душа: Знание → х1 FA Сожжение души → х1 Семя порчи → х2 Семя порчи → х3 Семя порчи → х4 Семя порчи → х5 Семя порчи → х6 Семя порчи → х7 FA Тёмная душа: Знание → х7 Семя порчи → х8 Семя порчи → х9 Семя порчи → х10 Семя порчи → х11 Семя порчи → х12 Семя порчи</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тёмная душа: Знание → х1 FA Сожжение души → х1 Семя порчи → х2 Семя порчи → х3 Семя порчи → х4 Семя порчи → х5 Семя порчи → х6 Семя порчи → х7 FA Тёмная душа: Знание → х7 Семя порчи → х8 Семя порчи → х9 Семя порчи → х10 Семя порчи → х11 Семя порчи → х12 Семя порчи</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Чернокнижник</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Демонология</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Метаморфоза → х1 Порча → х2 Стрела Тьмы → х3 Стрела Тьмы → х4 Стрела Тьмы → х5 Порча → х6 FA Метаморфоза → х6 Стрела Тьмы → х7 Стрела Тьмы → х8 Стрела Тьмы → х9 Порча → х10 Стрела Тьмы → х11 FA Метаморфоза → х11 Стрела Тьмы → х12 Стрела Тьмы</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Метаморфоза → х1 Буря Скверны (страж) → х2 Порча → х3 Стрела Тьмы → х4 Буря Скверны (страж) → х5 Длань Гул'дана → х6 FA Метаморфоза → х6 Порча → х7 Буря Скверны (страж) → х8 Стрела Тьмы → х9 Стрела Тьмы → х10 Буря Скверны (страж) → х11 FA Метаморфоза → х11 Длань Гул'дана → х12 Стрела Тьмы</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Метаморфоза → х1 Буря Скверны (страж) → х2 Порча → х3 Стрела Тьмы → х4 Буря Скверны (страж) → х5 Длань Гул'дана → х6 FA Метаморфоза → х6 Порча → х7 Буря Скверны (страж) → х8 Стрела Тьмы → х9 Стрела Тьмы → х10 Буря Скверны (страж) → х11 FA Метаморфоза → х11 Длань Гул'дана → х12 Стрела Тьмы</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Чернокнижник</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Разрушение</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>х1 Жертвенный огонь → х2 Поджигание → х3 Испепеление → х4 Жертвенный огонь → х5 Поджигание → х6 Испепеление → х7 Жертвенный огонь → х8 Поджигание → х9 Испепеление → х10 Жертвенный огонь → х11 Поджигание → х12 Испепеление</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>х1 Огненный ливень → х2 Огненный ливень → х3 Огненный ливень → х4 Огненный ливень → х5 Огненный ливень → х6 Огненный ливень → х7 Огненный ливень → х8 Огненный ливень → х9 Огненный ливень → х10 Огненный ливень → х11 Огненный ливень → х12 Огненный ливень</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>х1 Огненный ливень → х2 Огненный ливень → х3 Огненный ливень → х4 Огненный ливень → х5 Огненный ливень → х6 Огненный ливень → х7 Огненный ливень → х8 Огненный ливень → х9 Огненный ливень → х10 Огненный ливень → х11 Огненный ливень → х12 Огненный ливень</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Хмелевар</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар чёрного лотоса → х2 Джаб → х3 Джаб → х4 Удар чёрного лотоса → х5 Джаб → х6 Джаб → х7 Удар чёрного лотоса → х8 Джаб → х9 Джаб → х10 Удар чёрного лотоса → х11 Джаб → х12 Джаб</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар бочонком → х2 Танцующий журавль → х3 Танцующий журавль → х4 Удар бочонком → х5 Танцующий журавль → х6 Удар чёрного лотоса → х7 Удар бочонком → х8 Джаб → х9 Танцующий журавль → х10 Удар чёрного лотоса → х11 Удар бочонком → х12 Джаб</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>х1 Удар бочонком → х2 Танцующий журавль → х3 Танцующий журавль → х4 Удар бочонком → х5 Танцующий журавль → х6 Удар чёрного лотоса → х7 Удар бочонком → х8 Джаб → х9 Танцующий журавль → х10 Удар чёрного лотоса → х11 Удар бочонком → х12 Джаб</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Ткач туманов</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Призыв нефритовой змеи → х1 Удар нефритового лотоса → х2 Джаб → х3 Джаб → х4 Удар нефритового лотоса → х5 Джаб → х6 Джаб → х7 Удар нефритового лотоса → х8 FA Призыв нефритовой змеи → х8 Джаб → х9 Джаб → х10 Удар нефритового лотоса → х11 Джаб → х12 Джаб</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Призыв нефритовой змеи → х1 Танцующий журавль → х2 Танцующий журавль → х3 Танцующий журавль → х4 Танцующий журавль → х5 Танцующий журавль → х6 Танцующий журавль → х7 Танцующий журавль → х8 FA Призыв нефритовой змеи → х8 Танцующий журавль → х9 Танцующий журавль → х10 Танцующий журавль → х11 Танцующий журавль → х12 Танцующий журавль</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>х1 FA Призыв нефритовой змеи → х1 Танцующий журавль → х2 Танцующий журавль → х3 Танцующий журавль → х4 Танцующий журавль → х5 Танцующий журавль → х6 Танцующий журавль → х7 Танцующий журавль → х8 FA Призыв нефритовой змеи → х8 Танцующий журавль → х9 Танцующий журавль → х10 Танцующий журавль → х11 Танцующий журавль → х12 Танцующий журавль</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Монах</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Танцующий с ветром</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Пиво тигриного глаза → х1 Призыв Сюэня → х2 Лапа тигра → х3 Удар восходящего солнца → х4 FA Пиво тигриного глаза → х4 Лапа тигра → х5 Удар восходящего солнца → х6 Лапа тигра → х7 FA Пиво тигриного глаза → х7 Удар восходящего солнца → х8 Лапа тигра → х9 Удар восходящего солнца → х10 FA Пиво тигриного глаза → х10 Призыв Сюэня → х11 Лапа тигра → х12 Удар восходящего солнца</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Пиво тигриного глаза → х1 Танцующий журавль → х2 Танцующий журавль → х3 Танцующий журавль → х4 FA Пиво тигриного глаза → х4 Танцующий журавль → х5 Танцующий журавль → х6 Танцующий журавль → х7 FA Пиво тигриного глаза → х7 Танцующий журавль → х8 Танцующий журавль → х9 Танцующий журавль → х10 FA Пиво тигриного глаза → х10 Танцующий журавль → х11 Призыв Сюэня → х12 Танцующий журавль</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Пиво тигриного глаза → х1 Танцующий журавль → х2 Танцующий журавль → х3 Танцующий журавль → х4 FA Пиво тигриного глаза → х4 Танцующий журавль → х5 Танцующий журавль → х6 Танцующий журавль → х7 FA Пиво тигриного глаза → х7 Танцующий журавль → х8 Танцующий журавль → х9 Танцующий журавль → х10 FA Пиво тигриного глаза → х10 Танцующий журавль → х11 Призыв Сюэня → х12 Танцующий журавль</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Небесное выравнивание → х1 FA Воплощение → х1 Лунный огонь → х2 Солнечный огонь → х3 Звёздный поток → х4 Звёздный огонь → х5 Лунный огонь → х6 FA Небесное выравнивание → х6 Солнечный огонь → х7 FA Воплощение → х7 Звёздный поток → х8 Звёздный огонь → х9 Звёздный поток → х10 Лунный огонь → х11 FA Небесное выравнивание → х11 Звёздный поток</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Небесное выравнивание → х1 FA Воплощение → х1 Звездопад → х2 Ураган → х3 Ураган → х4 Звездопад → х5 Ураган → х6 FA Небесное выравнивание → х6 Ураган → х7 FA Воплощение → х7 Звездопад → х8 Ураган → х9 Ураган → х10 Звездопад → х11 FA Небесное выравнивание → х11 Ураган</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Небесное выравнивание → х1 FA Воплощение → х1 Звездопад → х2 Ураган → х3 Ураган → х4 Звездопад → х5 Ураган → х6 FA Небесное выравнивание → х6 Ураган → х7 FA Воплощение → х7 Звездопад → х8 Ураган → х9 Ураган → х10 Звездопад → х11 FA Небесное выравнивание → х11 Ураган</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Сила зверя</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тигриное неистовство → х1 FA Берсерк → х1 FA Дикий рёв → х1 Глубокая рана → х2 Полоснуть → х3 Полоснуть → х4 FA Тигриное неистовство → х4 Глубокая рана → х5 FA Дикий рёв → х5 Полоснуть → х6 FA Берсерк → х6 Свирепый укус → х7 FA Тигриное неистовство → х7 Глубокая рана → х8 Полоснуть → х9 FA Дикий рёв</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тигриное неистовство → х1 FA Берсерк → х1 FA Дикий рёв → х1 Взбучка → х2 Размах → х3 простой → х4 FA Тигриное неистовство → х4 Взбучка → х5 FA Дикий рёв → х5 Размах → х6 FA Берсерк → х6 простой → х7 FA Тигриное неистовство → х7 Взбучка → х8 Размах → х9 FA Дикий рёв</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Тигриное неистовство → х1 FA Берсерк → х1 FA Дикий рёв → х1 Взбучка → х2 Размах → х3 простой → х4 FA Тигриное неистовство → х4 Взбучка → х5 FA Дикий рёв → х5 Размах → х6 FA Берсерк → х6 простой → х7 FA Тигриное неистовство → х7 Взбучка → х8 Размах → х9 FA Дикий рёв</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Страж</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>х1 Трепка → х2 Трепка → х3 Увечье → х4 Растерзать → х5 Увечье → х6 Трепка → х7 Трепка → х8 Трепка → х9 Трепка → х10 Увечье → х11 Трепка → х12 Трепка</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>х1 Взбучка → х2 Растерзать → х3 Трепка → х4 Взбучка → х5 Трепка → х6 Трепка → х7 Взбучка → х8 Растерзать → х9 Увечье → х10 Взбучка → х11 Растерзать → х12 Трепка</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>х1 Взбучка → х2 Растерзать → х3 Трепка → х4 Взбучка → х5 Трепка → х6 Трепка → х7 Взбучка → х8 Растерзать → х9 Увечье → х10 Взбучка → х11 Растерзать → х12 Трепка</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>healer</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Друид</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Исцеление</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>х1 Лунный огонь → х2 Гнев → х3 Гнев → х4 Гнев → х5 Лунный огонь → х6 Гнев → х7 Гнев → х8 Гнев → х9 Лунный огонь → х10 Гнев → х11 Гнев → х12 Гнев</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>х1 Лунный огонь → х2 Гнев → х3 Гнев → х4 Гнев → х5 Лунный огонь → х6 Гнев → х7 Гнев → х8 Гнев → х9 Лунный огонь → х10 Гнев → х11 Гнев → х12 Гнев</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>х1 Лунный огонь → х2 Гнев → х3 Гнев → х4 Гнев → х5 Лунный огонь → х6 Гнев → х7 Гнев → х8 Гнев → х9 Лунный огонь → х10 Гнев → х11 Гнев → х12 Гнев</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Гном-инженер</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Механист</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Разгон → х1 Заклёпочный пистолет → х2 Заклёпочный пистолет → х3 Заклёпочный пистолет → х4 FA Разгон → х4 Удар гаечным ключом → х5 Удар гаечным ключом → х6 Заклёпочный пистолет → х7 FA Разгон → х7 Удар гаечным ключом → х8 Удар гаечным ключом → х9 Заклёпочный пистолет → х10 FA Разгон → х10 Удар гаечным ключом → х11 Заклёпочный пистолет → х12 Удар гаечным ключом</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Разгон → х1 Заклёпочный пистолет → х2 Заклёпочный пистолет → х3 Заклёпочный пистолет → х4 FA Разгон → х4 Удар гаечным ключом → х5 Удар гаечным ключом → х6 Заклёпочный пистолет → х7 FA Разгон → х7 Удар гаечным ключом → х8 Удар гаечным ключом → х9 Заклёпочный пистолет → х10 FA Разгон → х10 Удар гаечным ключом → х11 Заклёпочный пистолет → х12 Удар гаечным ключом</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Разгон → х1 Заклёпочный пистолет → х2 Заклёпочный пистолет → х3 Заклёпочный пистолет → х4 FA Разгон → х4 Удар гаечным ключом → х5 Удар гаечным ключом → х6 Заклёпочный пистолет → х7 FA Разгон → х7 Удар гаечным ключом → х8 Удар гаечным ключом → х9 Заклёпочный пистолет → х10 FA Разгон → х10 Удар гаечным ключом → х11 Заклёпочный пистолет → х12 Удар гаечным ключом</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Гном-инженер</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Сапёр</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Нитро-ускорители → х1 Дистанционный заряд → х2 Дистанционный заряд → х3 Дистанционный заряд → х4 Дистанционный заряд → х5 FA Нитро-ускорители → х5 Липкая бомба → х6 Дистанционный заряд → х7 Липкая бомба → х8 Дистанционный заряд → х9 FA Нитро-ускорители → х9 Липкая бомба → х10 Дистанционный заряд → х11 Липкая бомба → х12 Дистанционный заряд</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Нитро-ускорители → х1 Ракетный залп → х2 Кассетная бомба → х3 Липкая бомба → х4 Шрапнель → х5 Липкая бомба → х6 FA Нитро-ускорители → х6 Липкая бомба → х7 Шрапнель → х8 Липкая бомба → х9 Дистанционный заряд → х10 Липкая бомба → х11 FA Нитро-ускорители → х11 Липкая бомба → х12 Шрапнель</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>х1 FA Нитро-ускорители → х1 Ракетный залп → х2 Кассетная бомба → х3 Липкая бомба → х4 Шрапнель → х5 Липкая бомба → х6 FA Нитро-ускорители → х6 Липкая бомба → х7 Шрапнель → х8 Липкая бомба → х9 Дистанционный заряд → х10 Липкая бомба → х11 FA Нитро-ускорители → х11 Липкая бомба → х12 Шрапнель</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Гном-инженер</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Изобретатель</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>х1 Гномский луч смерти → х2 Поток флюкса → х3 Поток флюкса → х4 Поток флюкса → х5 Гномский луч смерти → х6 Поток флюкса → х7 Поток флюкса → х8 Поток флюкса → х9 Гномский луч смерти → х10 Поток флюкса → х11 Поток флюкса → х12 Поток флюкса</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>х1 Гномский луч смерти → х2 Поток флюкса → х3 Поток флюкса → х4 Поток флюкса → х5 Гномский луч смерти → х6 Поток флюкса → х7 Поток флюкса → х8 Поток флюкса → х9 Гномский луч смерти → х10 Поток флюкса → х11 Поток флюкса → х12 Поток флюкса</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>х1 Гномский луч смерти → х2 Поток флюкса → х3 Поток флюкса → х4 Поток флюкса → х5 Гномский луч смерти → х6 Поток флюкса → х7 Поток флюкса → х8 Поток флюкса → х9 Гномский луч смерти → х10 Поток флюкса → х11 Поток флюкса → х12 Поток флюкса</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F38"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>